--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
@@ -451,49 +451,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.398603495011786</v>
+        <v>0.398603495288631</v>
       </c>
       <c r="D2">
-        <v>0.5796215309538708</v>
+        <v>0.5796215308245597</v>
       </c>
       <c r="E2">
-        <v>0.6115443543940347</v>
+        <v>0.6115443544017672</v>
       </c>
       <c r="F2">
-        <v>0.6229120939490871</v>
+        <v>0.6229120938299625</v>
       </c>
       <c r="G2">
-        <v>0.6094901072200055</v>
+        <v>0.6094901072175753</v>
       </c>
       <c r="H2">
-        <v>0.6333952788413868</v>
+        <v>0.6333952788198499</v>
       </c>
       <c r="I2">
-        <v>0.6378565372190187</v>
+        <v>0.6378565366366508</v>
       </c>
       <c r="J2">
-        <v>0.616711841009653</v>
+        <v>0.6167118401602516</v>
       </c>
       <c r="K2">
-        <v>0.6269624440033628</v>
+        <v>0.6269624426194733</v>
       </c>
       <c r="L2">
-        <v>0.6077367071259279</v>
+        <v>0.6077367065273679</v>
       </c>
       <c r="M2">
-        <v>0.5965602976620978</v>
+        <v>0.5965602970734857</v>
       </c>
       <c r="N2">
-        <v>0.5512259691986484</v>
+        <v>0.5512259714194218</v>
       </c>
       <c r="O2">
-        <v>0.4899418299502862</v>
+        <v>0.4899418273956984</v>
       </c>
       <c r="P2">
-        <v>0.4346285606088682</v>
+        <v>0.4346285553972464</v>
       </c>
       <c r="Q2">
-        <v>0.4090620257545803</v>
+        <v>0.4090620296286822</v>
       </c>
     </row>
     <row r="3">
@@ -506,49 +506,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.4617014151424073</v>
+        <v>0.4617014107796591</v>
       </c>
       <c r="D3">
-        <v>0.5970153335015437</v>
+        <v>0.5970153342728549</v>
       </c>
       <c r="E3">
-        <v>0.5847151295184726</v>
+        <v>0.5847151305930663</v>
       </c>
       <c r="F3">
-        <v>0.5414156004513765</v>
+        <v>0.5414156061427675</v>
       </c>
       <c r="G3">
-        <v>0.57218006600289</v>
+        <v>0.5721800676545056</v>
       </c>
       <c r="H3">
-        <v>0.572126667696974</v>
+        <v>0.5721266732559012</v>
       </c>
       <c r="I3">
-        <v>0.5283849928401205</v>
+        <v>0.5283850042428816</v>
       </c>
       <c r="J3">
-        <v>0.5110956021363765</v>
+        <v>0.5110956178832888</v>
       </c>
       <c r="K3">
-        <v>0.463247882323941</v>
+        <v>0.4632479110495982</v>
       </c>
       <c r="L3">
-        <v>0.4444102361469563</v>
+        <v>0.4444102901054736</v>
       </c>
       <c r="M3">
-        <v>0.4180254343813385</v>
+        <v>0.418025524288794</v>
       </c>
       <c r="N3">
-        <v>0.3746319375996299</v>
+        <v>0.3746320583875278</v>
       </c>
       <c r="O3">
-        <v>0.3437547289082166</v>
+        <v>0.3437548981895753</v>
       </c>
       <c r="P3">
-        <v>0.3424860092376946</v>
+        <v>0.3424861771020791</v>
       </c>
       <c r="Q3">
-        <v>0.3607250247618591</v>
+        <v>0.3607251949075355</v>
       </c>
     </row>
     <row r="4">
@@ -561,49 +561,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.4215462238471482</v>
+        <v>0.4215462239794368</v>
       </c>
       <c r="D4">
-        <v>0.5676225425423789</v>
+        <v>0.5676225423991644</v>
       </c>
       <c r="E4">
-        <v>0.5775584725828261</v>
+        <v>0.5775584726869331</v>
       </c>
       <c r="F4">
-        <v>0.5893636719574695</v>
+        <v>0.5893636720793516</v>
       </c>
       <c r="G4">
-        <v>0.6000055092807184</v>
+        <v>0.6000055085191652</v>
       </c>
       <c r="H4">
-        <v>0.6365759437988273</v>
+        <v>0.6365759409314012</v>
       </c>
       <c r="I4">
-        <v>0.639163927112923</v>
+        <v>0.6391639251558272</v>
       </c>
       <c r="J4">
-        <v>0.628610880181693</v>
+        <v>0.6286108780380517</v>
       </c>
       <c r="K4">
-        <v>0.6099327624240019</v>
+        <v>0.609932757877123</v>
       </c>
       <c r="L4">
-        <v>0.5843241548221342</v>
+        <v>0.5843241481825473</v>
       </c>
       <c r="M4">
-        <v>0.5539149419763322</v>
+        <v>0.5539149304064234</v>
       </c>
       <c r="N4">
-        <v>0.4964997287565815</v>
+        <v>0.4964997200171531</v>
       </c>
       <c r="O4">
-        <v>0.4472110040074704</v>
+        <v>0.4472109998163881</v>
       </c>
       <c r="P4">
-        <v>0.4120940745849033</v>
+        <v>0.4120940729490042</v>
       </c>
       <c r="Q4">
-        <v>0.3770516311751237</v>
+        <v>0.3770516421620764</v>
       </c>
     </row>
     <row r="5">
@@ -616,49 +616,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.5905294755624082</v>
+        <v>0.5905294758379893</v>
       </c>
       <c r="D5">
-        <v>0.5981915554202726</v>
+        <v>0.598191556127219</v>
       </c>
       <c r="E5">
-        <v>0.6045045790507451</v>
+        <v>0.6045045797068034</v>
       </c>
       <c r="F5">
-        <v>0.6006516118084487</v>
+        <v>0.6006516126895849</v>
       </c>
       <c r="G5">
-        <v>0.6086788934441667</v>
+        <v>0.6086788952956078</v>
       </c>
       <c r="H5">
-        <v>0.606776384219445</v>
+        <v>0.6067763870467067</v>
       </c>
       <c r="I5">
-        <v>0.5890617907226202</v>
+        <v>0.589061793132282</v>
       </c>
       <c r="J5">
-        <v>0.5459926364876917</v>
+        <v>0.5459926428681074</v>
       </c>
       <c r="K5">
-        <v>0.4739255027035414</v>
+        <v>0.4739255027385437</v>
       </c>
       <c r="L5">
-        <v>0.4352985341614405</v>
+        <v>0.4352985285266296</v>
       </c>
       <c r="M5">
-        <v>0.4015295240755037</v>
+        <v>0.4015295173096729</v>
       </c>
       <c r="N5">
-        <v>0.3972988994666473</v>
+        <v>0.3972988967428645</v>
       </c>
       <c r="O5">
-        <v>0.4040897795225095</v>
+        <v>0.4040897867052587</v>
       </c>
       <c r="P5">
-        <v>0.4064016711740003</v>
+        <v>0.4064016818476489</v>
       </c>
       <c r="Q5">
-        <v>0.404993325409037</v>
+        <v>0.4049933359821918</v>
       </c>
     </row>
     <row r="6">
@@ -671,49 +671,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.5864256049358012</v>
+        <v>0.5864256052085073</v>
       </c>
       <c r="D6">
-        <v>0.5935788908407292</v>
+        <v>0.5935788918187332</v>
       </c>
       <c r="E6">
-        <v>0.6039908631011724</v>
+        <v>0.6039908645105515</v>
       </c>
       <c r="F6">
-        <v>0.6089097911532259</v>
+        <v>0.6089097933779206</v>
       </c>
       <c r="G6">
-        <v>0.6290467009621706</v>
+        <v>0.6290467038376087</v>
       </c>
       <c r="H6">
-        <v>0.6225151607013525</v>
+        <v>0.6225151633310956</v>
       </c>
       <c r="I6">
-        <v>0.5957963809010661</v>
+        <v>0.5957963851700675</v>
       </c>
       <c r="J6">
-        <v>0.5693968990328666</v>
+        <v>0.5693969025167809</v>
       </c>
       <c r="K6">
-        <v>0.5385332064928584</v>
+        <v>0.5385332036814814</v>
       </c>
       <c r="L6">
-        <v>0.5214438396402963</v>
+        <v>0.521443831529654</v>
       </c>
       <c r="M6">
-        <v>0.489361132552652</v>
+        <v>0.4893611195896905</v>
       </c>
       <c r="N6">
-        <v>0.4703783425760318</v>
+        <v>0.4703783395334761</v>
       </c>
       <c r="O6">
-        <v>0.4534980653519925</v>
+        <v>0.4534980582128631</v>
       </c>
       <c r="P6">
-        <v>0.4496461070298668</v>
+        <v>0.4496461056890905</v>
       </c>
       <c r="Q6">
-        <v>0.4374177385588689</v>
+        <v>0.437417741351489</v>
       </c>
     </row>
     <row r="7">
@@ -726,49 +726,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.4237376363433553</v>
+        <v>0.4237376365007877</v>
       </c>
       <c r="D7">
-        <v>0.5797804709016181</v>
+        <v>0.5797804707700887</v>
       </c>
       <c r="E7">
-        <v>0.6290760928983262</v>
+        <v>0.629076092866513</v>
       </c>
       <c r="F7">
-        <v>0.6372842679356893</v>
+        <v>0.637284268074697</v>
       </c>
       <c r="G7">
-        <v>0.6379197970331528</v>
+        <v>0.6379197971983536</v>
       </c>
       <c r="H7">
-        <v>0.646987070811315</v>
+        <v>0.6469870702968176</v>
       </c>
       <c r="I7">
-        <v>0.6374658916424079</v>
+        <v>0.6374658902149772</v>
       </c>
       <c r="J7">
-        <v>0.6387656202158222</v>
+        <v>0.6387656172937364</v>
       </c>
       <c r="K7">
-        <v>0.6231026941488707</v>
+        <v>0.6231026912804514</v>
       </c>
       <c r="L7">
-        <v>0.5992399548957057</v>
+        <v>0.5992399483229416</v>
       </c>
       <c r="M7">
-        <v>0.5741213981328667</v>
+        <v>0.5741213856400273</v>
       </c>
       <c r="N7">
-        <v>0.5151055361695721</v>
+        <v>0.5151055200689669</v>
       </c>
       <c r="O7">
-        <v>0.4702886143887231</v>
+        <v>0.4702886038758084</v>
       </c>
       <c r="P7">
-        <v>0.4206097948044066</v>
+        <v>0.4206097955608392</v>
       </c>
       <c r="Q7">
-        <v>0.3914791201438557</v>
+        <v>0.3914791183623219</v>
       </c>
     </row>
     <row r="8">
@@ -781,49 +781,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.4993576157248136</v>
+        <v>0.4993576155438536</v>
       </c>
       <c r="D8">
-        <v>0.5764728033376713</v>
+        <v>0.5764728031788809</v>
       </c>
       <c r="E8">
-        <v>0.6270923041613999</v>
+        <v>0.6270923046611112</v>
       </c>
       <c r="F8">
-        <v>0.638617316013244</v>
+        <v>0.6386173164328509</v>
       </c>
       <c r="G8">
-        <v>0.6459393664686576</v>
+        <v>0.6459393662318302</v>
       </c>
       <c r="H8">
-        <v>0.6293847729504991</v>
+        <v>0.6293847719183233</v>
       </c>
       <c r="I8">
-        <v>0.6278343407291129</v>
+        <v>0.6278343393386967</v>
       </c>
       <c r="J8">
-        <v>0.5981098229093306</v>
+        <v>0.5981098199115741</v>
       </c>
       <c r="K8">
-        <v>0.5531791167532928</v>
+        <v>0.5531791078374955</v>
       </c>
       <c r="L8">
-        <v>0.529599213432713</v>
+        <v>0.5295991999845328</v>
       </c>
       <c r="M8">
-        <v>0.5108858541575627</v>
+        <v>0.5108858305684637</v>
       </c>
       <c r="N8">
-        <v>0.473168630552142</v>
+        <v>0.4731685978271125</v>
       </c>
       <c r="O8">
-        <v>0.4061224310702001</v>
+        <v>0.4061224051349844</v>
       </c>
       <c r="P8">
-        <v>0.3565150070749667</v>
+        <v>0.3565149967697238</v>
       </c>
       <c r="Q8">
-        <v>0.3256260343490119</v>
+        <v>0.3256260384090546</v>
       </c>
     </row>
     <row r="9">
@@ -836,49 +836,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.4980348066975618</v>
+        <v>0.4980348065197885</v>
       </c>
       <c r="D9">
-        <v>0.5740107050761313</v>
+        <v>0.5740107049181028</v>
       </c>
       <c r="E9">
-        <v>0.6248304379267619</v>
+        <v>0.6248304384128449</v>
       </c>
       <c r="F9">
-        <v>0.6384518745722876</v>
+        <v>0.6384518750334458</v>
       </c>
       <c r="G9">
-        <v>0.6491209975360522</v>
+        <v>0.6491209971385019</v>
       </c>
       <c r="H9">
-        <v>0.6371793320637918</v>
+        <v>0.6371793311745546</v>
       </c>
       <c r="I9">
-        <v>0.6392130233742884</v>
+        <v>0.6392130223816563</v>
       </c>
       <c r="J9">
-        <v>0.6312315995968165</v>
+        <v>0.6312315980287481</v>
       </c>
       <c r="K9">
-        <v>0.6097434587923387</v>
+        <v>0.6097434556211977</v>
       </c>
       <c r="L9">
-        <v>0.5959070036561815</v>
+        <v>0.5959069978885631</v>
       </c>
       <c r="M9">
-        <v>0.5950464422264008</v>
+        <v>0.5950464242810951</v>
       </c>
       <c r="N9">
-        <v>0.583671124713479</v>
+        <v>0.5836711024940165</v>
       </c>
       <c r="O9">
-        <v>0.5530975582934453</v>
+        <v>0.5530975313831483</v>
       </c>
       <c r="P9">
-        <v>0.5354491004594927</v>
+        <v>0.5354490660997112</v>
       </c>
       <c r="Q9">
-        <v>0.5168898758492021</v>
+        <v>0.516889835934404</v>
       </c>
     </row>
     <row r="10">
@@ -891,49 +891,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.5001438566609585</v>
+        <v>0.5001438564801923</v>
       </c>
       <c r="D10">
-        <v>0.575747383557518</v>
+        <v>0.5757473834017426</v>
       </c>
       <c r="E10">
-        <v>0.626030842429744</v>
+        <v>0.6260308429297468</v>
       </c>
       <c r="F10">
-        <v>0.639675277225833</v>
+        <v>0.6396752776693123</v>
       </c>
       <c r="G10">
-        <v>0.6480397015468361</v>
+        <v>0.6480397012295885</v>
       </c>
       <c r="H10">
-        <v>0.636163030522737</v>
+        <v>0.6361630297195962</v>
       </c>
       <c r="I10">
-        <v>0.6390889266304092</v>
+        <v>0.6390889257052792</v>
       </c>
       <c r="J10">
-        <v>0.6321072653537733</v>
+        <v>0.6321072637427158</v>
       </c>
       <c r="K10">
-        <v>0.6129545079381332</v>
+        <v>0.6129545056217774</v>
       </c>
       <c r="L10">
-        <v>0.6003636467020448</v>
+        <v>0.6003636401994856</v>
       </c>
       <c r="M10">
-        <v>0.599798906868797</v>
+        <v>0.5997988905413378</v>
       </c>
       <c r="N10">
-        <v>0.5889343190354048</v>
+        <v>0.58893429127117</v>
       </c>
       <c r="O10">
-        <v>0.557233885964135</v>
+        <v>0.5572338527222908</v>
       </c>
       <c r="P10">
-        <v>0.5363409841546602</v>
+        <v>0.5363409520090223</v>
       </c>
       <c r="Q10">
-        <v>0.5117445250486772</v>
+        <v>0.5117444804333255</v>
       </c>
     </row>
     <row r="11">
@@ -946,49 +946,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.499725909870483</v>
+        <v>0.4997259096901235</v>
       </c>
       <c r="D11">
-        <v>0.5779786783326801</v>
+        <v>0.5779786781756561</v>
       </c>
       <c r="E11">
-        <v>0.6284199037103522</v>
+        <v>0.6284199041996327</v>
       </c>
       <c r="F11">
-        <v>0.6404968937853383</v>
+        <v>0.6404968942290221</v>
       </c>
       <c r="G11">
-        <v>0.6496560102291485</v>
+        <v>0.6496560099039261</v>
       </c>
       <c r="H11">
-        <v>0.6386965139368095</v>
+        <v>0.6386965128312287</v>
       </c>
       <c r="I11">
-        <v>0.6402215298307551</v>
+        <v>0.6402215281580792</v>
       </c>
       <c r="J11">
-        <v>0.6351517944607956</v>
+        <v>0.6351517918701541</v>
       </c>
       <c r="K11">
-        <v>0.6171994075087799</v>
+        <v>0.6171994025104879</v>
       </c>
       <c r="L11">
-        <v>0.6131980569778731</v>
+        <v>0.6131980485171891</v>
       </c>
       <c r="M11">
-        <v>0.6138146104506439</v>
+        <v>0.6138145954162879</v>
       </c>
       <c r="N11">
-        <v>0.6062125044734721</v>
+        <v>0.606212478943176</v>
       </c>
       <c r="O11">
-        <v>0.5758767856855294</v>
+        <v>0.575876754327061</v>
       </c>
       <c r="P11">
-        <v>0.5528038039065752</v>
+        <v>0.5528037693450353</v>
       </c>
       <c r="Q11">
-        <v>0.5379160002596108</v>
+        <v>0.5379159616250269</v>
       </c>
     </row>
     <row r="12">
@@ -1001,49 +1001,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.6051000095029837</v>
+        <v>0.6051000098473991</v>
       </c>
       <c r="D12">
-        <v>0.6151827290492567</v>
+        <v>0.6151827299557535</v>
       </c>
       <c r="E12">
-        <v>0.6230081594335577</v>
+        <v>0.6230081604628288</v>
       </c>
       <c r="F12">
-        <v>0.6236784946416618</v>
+        <v>0.6236784961274926</v>
       </c>
       <c r="G12">
-        <v>0.6261728412999161</v>
+        <v>0.6261728437839038</v>
       </c>
       <c r="H12">
-        <v>0.6258876930353688</v>
+        <v>0.6258876963662515</v>
       </c>
       <c r="I12">
-        <v>0.6052111361851702</v>
+        <v>0.6052111404748297</v>
       </c>
       <c r="J12">
-        <v>0.5639306619255363</v>
+        <v>0.5639306682732099</v>
       </c>
       <c r="K12">
-        <v>0.4993405266870967</v>
+        <v>0.4993405301937715</v>
       </c>
       <c r="L12">
-        <v>0.4400226248618244</v>
+        <v>0.4400226233681847</v>
       </c>
       <c r="M12">
-        <v>0.3719134458837232</v>
+        <v>0.3719134469652392</v>
       </c>
       <c r="N12">
-        <v>0.3456553183868946</v>
+        <v>0.3456553237604963</v>
       </c>
       <c r="O12">
-        <v>0.3531473134071786</v>
+        <v>0.3531473167611571</v>
       </c>
       <c r="P12">
-        <v>0.3590936518852654</v>
+        <v>0.3590936478696725</v>
       </c>
       <c r="Q12">
-        <v>0.3345172527736233</v>
+        <v>0.3345172342247513</v>
       </c>
     </row>
     <row r="13">
@@ -1056,49 +1056,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.6017763648084599</v>
+        <v>0.6017763648702028</v>
       </c>
       <c r="D13">
-        <v>0.598325304619442</v>
+        <v>0.5983253050573983</v>
       </c>
       <c r="E13">
-        <v>0.6107006601181375</v>
+        <v>0.6107006605862177</v>
       </c>
       <c r="F13">
-        <v>0.6217152221872957</v>
+        <v>0.6217152232416571</v>
       </c>
       <c r="G13">
-        <v>0.5817592587248596</v>
+        <v>0.5817592594994119</v>
       </c>
       <c r="H13">
-        <v>0.5622567425245549</v>
+        <v>0.5622567488976207</v>
       </c>
       <c r="I13">
-        <v>0.5613888640055945</v>
+        <v>0.5613888714537271</v>
       </c>
       <c r="J13">
-        <v>0.5476272051399351</v>
+        <v>0.5476272095233786</v>
       </c>
       <c r="K13">
-        <v>0.4753227471852248</v>
+        <v>0.4753227620953092</v>
       </c>
       <c r="L13">
-        <v>0.4093760998991058</v>
+        <v>0.4093761027938649</v>
       </c>
       <c r="M13">
-        <v>0.385895625438136</v>
+        <v>0.3858956255608932</v>
       </c>
       <c r="N13">
-        <v>0.3846510861913531</v>
+        <v>0.3846510885131632</v>
       </c>
       <c r="O13">
-        <v>0.3617976302076865</v>
+        <v>0.3617976253495353</v>
       </c>
       <c r="P13">
-        <v>0.3560396188236627</v>
+        <v>0.3560396266091589</v>
       </c>
       <c r="Q13">
-        <v>0.3218966079262589</v>
+        <v>0.3218966353645266</v>
       </c>
     </row>
     <row r="14">
@@ -1111,49 +1111,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.4259866773691758</v>
+        <v>0.4259866775211756</v>
       </c>
       <c r="D14">
-        <v>0.5788855496486157</v>
+        <v>0.5788855495331494</v>
       </c>
       <c r="E14">
-        <v>0.6265842503391412</v>
+        <v>0.6265842503305433</v>
       </c>
       <c r="F14">
-        <v>0.6363031620127618</v>
+        <v>0.6363031621768244</v>
       </c>
       <c r="G14">
-        <v>0.637168258726418</v>
+        <v>0.6371682589084904</v>
       </c>
       <c r="H14">
-        <v>0.6513511554313515</v>
+        <v>0.6513511549353476</v>
       </c>
       <c r="I14">
-        <v>0.6395466321422894</v>
+        <v>0.6395466308090545</v>
       </c>
       <c r="J14">
-        <v>0.6432820255965533</v>
+        <v>0.6432820231142474</v>
       </c>
       <c r="K14">
-        <v>0.6384006947307795</v>
+        <v>0.6384006922296377</v>
       </c>
       <c r="L14">
-        <v>0.6250744182237202</v>
+        <v>0.6250744130780642</v>
       </c>
       <c r="M14">
-        <v>0.6214878063881102</v>
+        <v>0.6214878142483484</v>
       </c>
       <c r="N14">
-        <v>0.5966179309399365</v>
+        <v>0.5966177302613578</v>
       </c>
       <c r="O14">
-        <v>0.5686812365904859</v>
+        <v>0.56868119558305</v>
       </c>
       <c r="P14">
-        <v>0.5307024975454619</v>
+        <v>0.5307024624650931</v>
       </c>
       <c r="Q14">
-        <v>0.4817706674435866</v>
+        <v>0.4817706407640922</v>
       </c>
     </row>
     <row r="15">
@@ -1166,49 +1166,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.426582304168972</v>
+        <v>0.4265823043187869</v>
       </c>
       <c r="D15">
-        <v>0.5806889119271192</v>
+        <v>0.5806889118098054</v>
       </c>
       <c r="E15">
-        <v>0.628141816395726</v>
+        <v>0.6281418164179143</v>
       </c>
       <c r="F15">
-        <v>0.6363369524474436</v>
+        <v>0.6363369526434711</v>
       </c>
       <c r="G15">
-        <v>0.6378467126661298</v>
+        <v>0.6378467128291959</v>
       </c>
       <c r="H15">
-        <v>0.6458420352814049</v>
+        <v>0.6458420347786481</v>
       </c>
       <c r="I15">
-        <v>0.6395098093529729</v>
+        <v>0.6395098079861467</v>
       </c>
       <c r="J15">
-        <v>0.6444741665038215</v>
+        <v>0.6444741640662915</v>
       </c>
       <c r="K15">
-        <v>0.6455478638604474</v>
+        <v>0.6455478615751734</v>
       </c>
       <c r="L15">
-        <v>0.6306475204323497</v>
+        <v>0.6306475180140872</v>
       </c>
       <c r="M15">
-        <v>0.6261437395520019</v>
+        <v>0.6261437354887247</v>
       </c>
       <c r="N15">
-        <v>0.6036634207492984</v>
+        <v>0.6036634089986597</v>
       </c>
       <c r="O15">
-        <v>0.5703108351178851</v>
+        <v>0.5703108106724142</v>
       </c>
       <c r="P15">
-        <v>0.5479881281384356</v>
+        <v>0.5479880965987717</v>
       </c>
       <c r="Q15">
-        <v>0.5335676259700074</v>
+        <v>0.5335675921304046</v>
       </c>
     </row>
     <row r="16">
@@ -1221,49 +1221,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.428316045949979</v>
+        <v>0.4283160461134877</v>
       </c>
       <c r="D16">
-        <v>0.5813165641942674</v>
+        <v>0.581316564077342</v>
       </c>
       <c r="E16">
-        <v>0.6303489025766604</v>
+        <v>0.6303489025645743</v>
       </c>
       <c r="F16">
-        <v>0.6391117153933984</v>
+        <v>0.6391117155657522</v>
       </c>
       <c r="G16">
-        <v>0.6401182669737909</v>
+        <v>0.640118267083967</v>
       </c>
       <c r="H16">
-        <v>0.6522391825315378</v>
+        <v>0.6522391819617206</v>
       </c>
       <c r="I16">
-        <v>0.6416777042578031</v>
+        <v>0.6416777027466827</v>
       </c>
       <c r="J16">
-        <v>0.6443647177612216</v>
+        <v>0.6443647149624139</v>
       </c>
       <c r="K16">
-        <v>0.6398027348383444</v>
+        <v>0.6398027317047205</v>
       </c>
       <c r="L16">
-        <v>0.6273511222868448</v>
+        <v>0.627351118094336</v>
       </c>
       <c r="M16">
-        <v>0.623190331150643</v>
+        <v>0.6231903441137577</v>
       </c>
       <c r="N16">
-        <v>0.591504181022092</v>
+        <v>0.591504060647724</v>
       </c>
       <c r="O16">
-        <v>0.5516242912197713</v>
+        <v>0.5516241930013434</v>
       </c>
       <c r="P16">
-        <v>0.5223385003622713</v>
+        <v>0.5223384641283746</v>
       </c>
       <c r="Q16">
-        <v>0.5113977505331011</v>
+        <v>0.5113977085784156</v>
       </c>
     </row>
     <row r="17">
@@ -1276,49 +1276,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.425414093594182</v>
+        <v>0.4254140937521366</v>
       </c>
       <c r="D17">
-        <v>0.5799663772002934</v>
+        <v>0.5799663770770407</v>
       </c>
       <c r="E17">
-        <v>0.6284166136780801</v>
+        <v>0.6284166136793</v>
       </c>
       <c r="F17">
-        <v>0.6374476312687694</v>
+        <v>0.6374476314334129</v>
       </c>
       <c r="G17">
-        <v>0.6386483778135</v>
+        <v>0.6386483779276955</v>
       </c>
       <c r="H17">
-        <v>0.6489561298372426</v>
+        <v>0.6489561294207166</v>
       </c>
       <c r="I17">
-        <v>0.6431639786747028</v>
+        <v>0.6431639772971526</v>
       </c>
       <c r="J17">
-        <v>0.6465567794211955</v>
+        <v>0.6465567770777291</v>
       </c>
       <c r="K17">
-        <v>0.6423666945935415</v>
+        <v>0.6423666920596968</v>
       </c>
       <c r="L17">
-        <v>0.6315985783848117</v>
+        <v>0.6315985745445086</v>
       </c>
       <c r="M17">
-        <v>0.6284865556975443</v>
+        <v>0.6284865495406007</v>
       </c>
       <c r="N17">
-        <v>0.5980455456995405</v>
+        <v>0.5980455322956706</v>
       </c>
       <c r="O17">
-        <v>0.5632134588008192</v>
+        <v>0.5632134277239086</v>
       </c>
       <c r="P17">
-        <v>0.5307725051788302</v>
+        <v>0.5307724606787082</v>
       </c>
       <c r="Q17">
-        <v>0.5239530228168146</v>
+        <v>0.5239529822483884</v>
       </c>
     </row>
     <row r="18">
@@ -1331,49 +1331,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.6048280275615323</v>
+        <v>0.6048280278842164</v>
       </c>
       <c r="D18">
-        <v>0.6132125453901094</v>
+        <v>0.6132125461754889</v>
       </c>
       <c r="E18">
-        <v>0.6174224091509803</v>
+        <v>0.6174224099286715</v>
       </c>
       <c r="F18">
-        <v>0.6141245868084009</v>
+        <v>0.6141245878936162</v>
       </c>
       <c r="G18">
-        <v>0.6254506645065848</v>
+        <v>0.625450666457595</v>
       </c>
       <c r="H18">
-        <v>0.6112325596599963</v>
+        <v>0.6112325626022511</v>
       </c>
       <c r="I18">
-        <v>0.5990669656960811</v>
+        <v>0.5990669699711547</v>
       </c>
       <c r="J18">
-        <v>0.5638008815597547</v>
+        <v>0.5638008855919032</v>
       </c>
       <c r="K18">
-        <v>0.5085604627778048</v>
+        <v>0.5085604677525242</v>
       </c>
       <c r="L18">
-        <v>0.4528816169458693</v>
+        <v>0.4528816148081412</v>
       </c>
       <c r="M18">
-        <v>0.4036717779086803</v>
+        <v>0.4036717758327261</v>
       </c>
       <c r="N18">
-        <v>0.3803605297511429</v>
+        <v>0.3803605318853507</v>
       </c>
       <c r="O18">
-        <v>0.3829515780051978</v>
+        <v>0.3829515879148847</v>
       </c>
       <c r="P18">
-        <v>0.3856053403727036</v>
+        <v>0.3856053533625796</v>
       </c>
       <c r="Q18">
-        <v>0.3876453328147946</v>
+        <v>0.3876453545824327</v>
       </c>
     </row>
     <row r="19">
@@ -1386,49 +1386,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.6035260226801238</v>
+        <v>0.6035260230135787</v>
       </c>
       <c r="D19">
-        <v>0.6125445767937102</v>
+        <v>0.6125445779415638</v>
       </c>
       <c r="E19">
-        <v>0.6251954338299706</v>
+        <v>0.6251954353705453</v>
       </c>
       <c r="F19">
-        <v>0.631793468497566</v>
+        <v>0.6317934706086885</v>
       </c>
       <c r="G19">
-        <v>0.6490901607129477</v>
+        <v>0.6490901631293208</v>
       </c>
       <c r="H19">
-        <v>0.6256713141672268</v>
+        <v>0.6256713171632933</v>
       </c>
       <c r="I19">
-        <v>0.6248825765472829</v>
+        <v>0.6248825789529077</v>
       </c>
       <c r="J19">
-        <v>0.597833241393123</v>
+        <v>0.5978332441133322</v>
       </c>
       <c r="K19">
-        <v>0.5674346315954505</v>
+        <v>0.5674346316461001</v>
       </c>
       <c r="L19">
-        <v>0.5300060466212377</v>
+        <v>0.5300060391269682</v>
       </c>
       <c r="M19">
-        <v>0.4939871825334476</v>
+        <v>0.4939871734830261</v>
       </c>
       <c r="N19">
-        <v>0.4722500957525277</v>
+        <v>0.4722500930028244</v>
       </c>
       <c r="O19">
-        <v>0.4490855669258114</v>
+        <v>0.449085572847302</v>
       </c>
       <c r="P19">
-        <v>0.438766961381643</v>
+        <v>0.4387669770594776</v>
       </c>
       <c r="Q19">
-        <v>0.4200046458487685</v>
+        <v>0.4200046817305113</v>
       </c>
     </row>
     <row r="20">
@@ -1441,49 +1441,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.6027578627871766</v>
+        <v>0.6027578629939608</v>
       </c>
       <c r="D20">
-        <v>0.6180968301972832</v>
+        <v>0.6180968310477329</v>
       </c>
       <c r="E20">
-        <v>0.6363694576856784</v>
+        <v>0.6363694590648233</v>
       </c>
       <c r="F20">
-        <v>0.6384660344500601</v>
+        <v>0.6384660360902915</v>
       </c>
       <c r="G20">
-        <v>0.6499411537076493</v>
+        <v>0.6499411549892145</v>
       </c>
       <c r="H20">
-        <v>0.6500919321258721</v>
+        <v>0.6500919328757052</v>
       </c>
       <c r="I20">
-        <v>0.6344770703052395</v>
+        <v>0.6344770731502605</v>
       </c>
       <c r="J20">
-        <v>0.604108092770223</v>
+        <v>0.6041080901604421</v>
       </c>
       <c r="K20">
-        <v>0.5813513405686792</v>
+        <v>0.5813513280500652</v>
       </c>
       <c r="L20">
-        <v>0.5697630735988712</v>
+        <v>0.5697630610207722</v>
       </c>
       <c r="M20">
-        <v>0.5422588137568572</v>
+        <v>0.5422587934921683</v>
       </c>
       <c r="N20">
-        <v>0.5207899725358203</v>
+        <v>0.5207899516909357</v>
       </c>
       <c r="O20">
-        <v>0.5157607058078953</v>
+        <v>0.5157606930561089</v>
       </c>
       <c r="P20">
-        <v>0.4928270958398208</v>
+        <v>0.4928271029398635</v>
       </c>
       <c r="Q20">
-        <v>0.4722141956514787</v>
+        <v>0.4722142361540881</v>
       </c>
     </row>
     <row r="21">
@@ -1496,49 +1496,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.4594094967201821</v>
+        <v>0.4594094919896185</v>
       </c>
       <c r="D21">
-        <v>0.5917621620045774</v>
+        <v>0.5917621624770708</v>
       </c>
       <c r="E21">
-        <v>0.5773449418066126</v>
+        <v>0.5773449424015602</v>
       </c>
       <c r="F21">
-        <v>0.5365997377830849</v>
+        <v>0.5365997418673072</v>
       </c>
       <c r="G21">
-        <v>0.5694354552847616</v>
+        <v>0.5694354545618674</v>
       </c>
       <c r="H21">
-        <v>0.5576961020148301</v>
+        <v>0.5576961003548669</v>
       </c>
       <c r="I21">
-        <v>0.4988121814989039</v>
+        <v>0.4988121865818193</v>
       </c>
       <c r="J21">
-        <v>0.4332271354968424</v>
+        <v>0.4332271357994179</v>
       </c>
       <c r="K21">
-        <v>0.4135817208280108</v>
+        <v>0.4135817155424485</v>
       </c>
       <c r="L21">
-        <v>0.379157856814734</v>
+        <v>0.3791578491959781</v>
       </c>
       <c r="M21">
-        <v>0.3669193569855166</v>
+        <v>0.3669193639487042</v>
       </c>
       <c r="N21">
-        <v>0.3584796034121402</v>
+        <v>0.3584796444055692</v>
       </c>
       <c r="O21">
-        <v>0.358657109321518</v>
+        <v>0.3586571761052978</v>
       </c>
       <c r="P21">
-        <v>0.3662511898578257</v>
+        <v>0.3662512452329014</v>
       </c>
       <c r="Q21">
-        <v>0.3496131153966723</v>
+        <v>0.3496131589380351</v>
       </c>
     </row>
     <row r="22">
@@ -1551,49 +1551,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.4585224463223009</v>
+        <v>0.4585224416135819</v>
       </c>
       <c r="D22">
-        <v>0.5922650287191309</v>
+        <v>0.592265029205132</v>
       </c>
       <c r="E22">
-        <v>0.5795517816912952</v>
+        <v>0.5795517822341977</v>
       </c>
       <c r="F22">
-        <v>0.5327466401852715</v>
+        <v>0.5327466444667849</v>
       </c>
       <c r="G22">
-        <v>0.5728129017844955</v>
+        <v>0.5728129015073971</v>
       </c>
       <c r="H22">
-        <v>0.5733642259025805</v>
+        <v>0.5733642193218943</v>
       </c>
       <c r="I22">
-        <v>0.5086481354375327</v>
+        <v>0.5086481414540436</v>
       </c>
       <c r="J22">
-        <v>0.4527241006196184</v>
+        <v>0.4527241142240094</v>
       </c>
       <c r="K22">
-        <v>0.4211246233507139</v>
+        <v>0.4211246497586936</v>
       </c>
       <c r="L22">
-        <v>0.4048716853945379</v>
+        <v>0.4048717309245515</v>
       </c>
       <c r="M22">
-        <v>0.377273312417102</v>
+        <v>0.3772733847023861</v>
       </c>
       <c r="N22">
-        <v>0.3733434522000036</v>
+        <v>0.3733436118642536</v>
       </c>
       <c r="O22">
-        <v>0.3781146936590822</v>
+        <v>0.3781148961812735</v>
       </c>
       <c r="P22">
-        <v>0.3803303859355568</v>
+        <v>0.3803306126783735</v>
       </c>
       <c r="Q22">
-        <v>0.3491629838298661</v>
+        <v>0.3491632236332814</v>
       </c>
     </row>
     <row r="23">
@@ -1606,49 +1606,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.5986823751912357</v>
+        <v>0.5986823748766439</v>
       </c>
       <c r="D23">
-        <v>0.5967550790986996</v>
+        <v>0.5967550789903154</v>
       </c>
       <c r="E23">
-        <v>0.5767383474364214</v>
+        <v>0.5767383484498408</v>
       </c>
       <c r="F23">
-        <v>0.5993398950115182</v>
+        <v>0.5993398930892981</v>
       </c>
       <c r="G23">
-        <v>0.5407008956124489</v>
+        <v>0.5407008430522319</v>
       </c>
       <c r="H23">
-        <v>0.4877450919148572</v>
+        <v>0.4877450806761628</v>
       </c>
       <c r="I23">
-        <v>0.427686584466544</v>
+        <v>0.4276865509386583</v>
       </c>
       <c r="J23">
-        <v>0.4098257213324562</v>
+        <v>0.4098256678929973</v>
       </c>
       <c r="K23">
-        <v>0.4242356891821279</v>
+        <v>0.424235615913058</v>
       </c>
       <c r="L23">
-        <v>0.381739865475829</v>
+        <v>0.3817397687217724</v>
       </c>
       <c r="M23">
-        <v>0.3563541371338694</v>
+        <v>0.3563539349760688</v>
       </c>
       <c r="N23">
-        <v>0.3333556180296163</v>
+        <v>0.3333552729662472</v>
       </c>
       <c r="O23">
-        <v>0.3084708376245854</v>
+        <v>0.3084703342384907</v>
       </c>
       <c r="P23">
-        <v>0.2967073881625283</v>
+        <v>0.2967068028997719</v>
       </c>
       <c r="Q23">
-        <v>0.2671532111969103</v>
+        <v>0.2671524583229998</v>
       </c>
     </row>
     <row r="24">
@@ -1661,49 +1661,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.5934885223214688</v>
+        <v>0.5934885223458384</v>
       </c>
       <c r="D24">
-        <v>0.6258504372193241</v>
+        <v>0.6258504371301894</v>
       </c>
       <c r="E24">
-        <v>0.6017023910180581</v>
+        <v>0.6017023913037026</v>
       </c>
       <c r="F24">
-        <v>0.6209745694250984</v>
+        <v>0.6209745691263406</v>
       </c>
       <c r="G24">
-        <v>0.6176128291677047</v>
+        <v>0.6176128291583023</v>
       </c>
       <c r="H24">
-        <v>0.6220736538754028</v>
+        <v>0.6220736525080853</v>
       </c>
       <c r="I24">
-        <v>0.6086577868072386</v>
+        <v>0.6086577856202452</v>
       </c>
       <c r="J24">
-        <v>0.5867579546165964</v>
+        <v>0.5867579442047997</v>
       </c>
       <c r="K24">
-        <v>0.5941106729750146</v>
+        <v>0.5941106759017265</v>
       </c>
       <c r="L24">
-        <v>0.5854319288143235</v>
+        <v>0.5854319434291901</v>
       </c>
       <c r="M24">
-        <v>0.5626108741672166</v>
+        <v>0.5626109118364971</v>
       </c>
       <c r="N24">
-        <v>0.5087939235329731</v>
+        <v>0.5087939999628466</v>
       </c>
       <c r="O24">
-        <v>0.4771745486594925</v>
+        <v>0.4771746521076722</v>
       </c>
       <c r="P24">
-        <v>0.4144713933144742</v>
+        <v>0.4144715563357911</v>
       </c>
       <c r="Q24">
-        <v>0.3518792851084365</v>
+        <v>0.3518794525368596</v>
       </c>
     </row>
     <row r="25">
@@ -1716,49 +1716,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.5972785101075291</v>
+        <v>0.597278510126438</v>
       </c>
       <c r="D25">
-        <v>0.6293092126345329</v>
+        <v>0.6293092125497199</v>
       </c>
       <c r="E25">
-        <v>0.604351580133934</v>
+        <v>0.6043515803768907</v>
       </c>
       <c r="F25">
-        <v>0.6225059580134844</v>
+        <v>0.622505957955782</v>
       </c>
       <c r="G25">
-        <v>0.6118472301642182</v>
+        <v>0.611847229922898</v>
       </c>
       <c r="H25">
-        <v>0.5906463178018146</v>
+        <v>0.5906463166702735</v>
       </c>
       <c r="I25">
-        <v>0.5617118212276521</v>
+        <v>0.5617118190575814</v>
       </c>
       <c r="J25">
-        <v>0.5666825876818999</v>
+        <v>0.5666825810560977</v>
       </c>
       <c r="K25">
-        <v>0.5717386242421354</v>
+        <v>0.5717386273416948</v>
       </c>
       <c r="L25">
-        <v>0.5817932866474412</v>
+        <v>0.5817933008478881</v>
       </c>
       <c r="M25">
-        <v>0.5629827626310441</v>
+        <v>0.5629827885284283</v>
       </c>
       <c r="N25">
-        <v>0.5337867039550176</v>
+        <v>0.5337867827745277</v>
       </c>
       <c r="O25">
-        <v>0.4891000991504086</v>
+        <v>0.4891002117547597</v>
       </c>
       <c r="P25">
-        <v>0.4527739929027468</v>
+        <v>0.4527741336750511</v>
       </c>
       <c r="Q25">
-        <v>0.3861000846123437</v>
+        <v>0.3861002801593135</v>
       </c>
     </row>
     <row r="26">
@@ -1771,49 +1771,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.6253818160041873</v>
+        <v>0.6253818159571509</v>
       </c>
       <c r="D26">
-        <v>0.6292621450337401</v>
+        <v>0.6292621449314934</v>
       </c>
       <c r="E26">
-        <v>0.6066493380222926</v>
+        <v>0.6066493378671561</v>
       </c>
       <c r="F26">
-        <v>0.6247573198780786</v>
+        <v>0.6247573194844889</v>
       </c>
       <c r="G26">
-        <v>0.6198159138617596</v>
+        <v>0.6198159133077619</v>
       </c>
       <c r="H26">
-        <v>0.624636916538303</v>
+        <v>0.6246369152301146</v>
       </c>
       <c r="I26">
-        <v>0.6078651961448228</v>
+        <v>0.6078651943382766</v>
       </c>
       <c r="J26">
-        <v>0.5877667929361369</v>
+        <v>0.587766789432583</v>
       </c>
       <c r="K26">
-        <v>0.5827428790418099</v>
+        <v>0.58274288418013</v>
       </c>
       <c r="L26">
-        <v>0.57303436264969</v>
+        <v>0.5730343905513177</v>
       </c>
       <c r="M26">
-        <v>0.5337226709850578</v>
+        <v>0.5337227357912389</v>
       </c>
       <c r="N26">
-        <v>0.493737014634747</v>
+        <v>0.4937371050196527</v>
       </c>
       <c r="O26">
-        <v>0.4346803976452118</v>
+        <v>0.4346805198799068</v>
       </c>
       <c r="P26">
-        <v>0.3755868763995021</v>
+        <v>0.3755870377148071</v>
       </c>
       <c r="Q26">
-        <v>0.2722154700109565</v>
+        <v>0.2722156546974768</v>
       </c>
     </row>
     <row r="27">
@@ -1826,49 +1826,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>0.6253737102441186</v>
+        <v>0.6253737102006008</v>
       </c>
       <c r="D27">
-        <v>0.6286354264906843</v>
+        <v>0.6286354263837762</v>
       </c>
       <c r="E27">
-        <v>0.6073370634487254</v>
+        <v>0.6073370632417774</v>
       </c>
       <c r="F27">
-        <v>0.6243918463438123</v>
+        <v>0.6243918458889819</v>
       </c>
       <c r="G27">
-        <v>0.6220316335922121</v>
+        <v>0.6220316328372508</v>
       </c>
       <c r="H27">
-        <v>0.6259372920788489</v>
+        <v>0.6259372902415432</v>
       </c>
       <c r="I27">
-        <v>0.6203358226392128</v>
+        <v>0.6203358198963504</v>
       </c>
       <c r="J27">
-        <v>0.613606105003614</v>
+        <v>0.613606099273394</v>
       </c>
       <c r="K27">
-        <v>0.6214616222961766</v>
+        <v>0.6214616098099485</v>
       </c>
       <c r="L27">
-        <v>0.6286702279020031</v>
+        <v>0.6286702214437259</v>
       </c>
       <c r="M27">
-        <v>0.6244246597706591</v>
+        <v>0.6244246572365714</v>
       </c>
       <c r="N27">
-        <v>0.6084071825857746</v>
+        <v>0.6084071755094116</v>
       </c>
       <c r="O27">
-        <v>0.5766175356602479</v>
+        <v>0.5766175406203091</v>
       </c>
       <c r="P27">
-        <v>0.5692240128230974</v>
+        <v>0.569224037799048</v>
       </c>
       <c r="Q27">
-        <v>0.4931352187780187</v>
+        <v>0.4931352379319821</v>
       </c>
     </row>
     <row r="28">
@@ -1881,49 +1881,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.5979660677624783</v>
+        <v>0.5979660677845973</v>
       </c>
       <c r="D28">
-        <v>0.6298139121999458</v>
+        <v>0.6298139121145794</v>
       </c>
       <c r="E28">
-        <v>0.6035210142959742</v>
+        <v>0.6035210145315298</v>
       </c>
       <c r="F28">
-        <v>0.6223056877541866</v>
+        <v>0.6223056875337432</v>
       </c>
       <c r="G28">
-        <v>0.6109722231908266</v>
+        <v>0.6109722230919871</v>
       </c>
       <c r="H28">
-        <v>0.5942075462530816</v>
+        <v>0.5942075459372904</v>
       </c>
       <c r="I28">
-        <v>0.574245173534681</v>
+        <v>0.5742451716673724</v>
       </c>
       <c r="J28">
-        <v>0.5893812613166354</v>
+        <v>0.589381251160737</v>
       </c>
       <c r="K28">
-        <v>0.5917405174755618</v>
+        <v>0.5917405102892508</v>
       </c>
       <c r="L28">
-        <v>0.6087455655997113</v>
+        <v>0.6087455609278054</v>
       </c>
       <c r="M28">
-        <v>0.6038632603998236</v>
+        <v>0.6038632530708261</v>
       </c>
       <c r="N28">
-        <v>0.5899063124772749</v>
+        <v>0.5899063104473617</v>
       </c>
       <c r="O28">
-        <v>0.5591888322778202</v>
+        <v>0.5591888347981032</v>
       </c>
       <c r="P28">
-        <v>0.552172389567211</v>
+        <v>0.5521723924084179</v>
       </c>
       <c r="Q28">
-        <v>0.5135090394615178</v>
+        <v>0.5135090850368411</v>
       </c>
     </row>
     <row r="29">
@@ -1936,49 +1936,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.5967554722830209</v>
+        <v>0.5967554723133834</v>
       </c>
       <c r="D29">
-        <v>0.6292448430559687</v>
+        <v>0.6292448429760226</v>
       </c>
       <c r="E29">
-        <v>0.6035937861420456</v>
+        <v>0.6035937864364849</v>
       </c>
       <c r="F29">
-        <v>0.6208259147787204</v>
+        <v>0.6208259146835858</v>
       </c>
       <c r="G29">
-        <v>0.6108141879716894</v>
+        <v>0.6108141881731151</v>
       </c>
       <c r="H29">
-        <v>0.5949856691770429</v>
+        <v>0.5949856686392656</v>
       </c>
       <c r="I29">
-        <v>0.5761287914708833</v>
+        <v>0.5761287911484779</v>
       </c>
       <c r="J29">
-        <v>0.5871704458927809</v>
+        <v>0.5871704377825026</v>
       </c>
       <c r="K29">
-        <v>0.5883575966688835</v>
+        <v>0.588357590796874</v>
       </c>
       <c r="L29">
-        <v>0.6055704404911495</v>
+        <v>0.6055704347861968</v>
       </c>
       <c r="M29">
-        <v>0.6034246289846346</v>
+        <v>0.6034246237154982</v>
       </c>
       <c r="N29">
-        <v>0.5951937542239877</v>
+        <v>0.5951937568430841</v>
       </c>
       <c r="O29">
-        <v>0.5679469680102267</v>
+        <v>0.5679469707445851</v>
       </c>
       <c r="P29">
-        <v>0.5657044679676012</v>
+        <v>0.565704473986841</v>
       </c>
       <c r="Q29">
-        <v>0.5276548358348159</v>
+        <v>0.5276548775699419</v>
       </c>
     </row>
     <row r="30">
@@ -1991,49 +1991,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.597190857656735</v>
+        <v>0.597190857681116</v>
       </c>
       <c r="D30">
-        <v>0.6295655152078538</v>
+        <v>0.6295655151228073</v>
       </c>
       <c r="E30">
-        <v>0.6056640477958737</v>
+        <v>0.6056640479764894</v>
       </c>
       <c r="F30">
-        <v>0.6255503326917495</v>
+        <v>0.6255503325302429</v>
       </c>
       <c r="G30">
-        <v>0.6156284140288003</v>
+        <v>0.6156284140064616</v>
       </c>
       <c r="H30">
-        <v>0.6013513047779631</v>
+        <v>0.6013513041593674</v>
       </c>
       <c r="I30">
-        <v>0.5852136116242659</v>
+        <v>0.5852136101243813</v>
       </c>
       <c r="J30">
-        <v>0.6005242296045683</v>
+        <v>0.600524218815619</v>
       </c>
       <c r="K30">
-        <v>0.6021066238035712</v>
+        <v>0.6021066186162359</v>
       </c>
       <c r="L30">
-        <v>0.6136754060745586</v>
+        <v>0.6136753999739003</v>
       </c>
       <c r="M30">
-        <v>0.6130932689383987</v>
+        <v>0.6130932564595177</v>
       </c>
       <c r="N30">
-        <v>0.607695152902066</v>
+        <v>0.607695150706</v>
       </c>
       <c r="O30">
-        <v>0.5830104642593321</v>
+        <v>0.5830104580296128</v>
       </c>
       <c r="P30">
-        <v>0.5795103693884839</v>
+        <v>0.5795103288736759</v>
       </c>
       <c r="Q30">
-        <v>0.5459966392545235</v>
+        <v>0.5459966703065601</v>
       </c>
     </row>
     <row r="31">
@@ -2046,49 +2046,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.5983343541481473</v>
+        <v>0.5983343541723485</v>
       </c>
       <c r="D31">
-        <v>0.6309010242390727</v>
+        <v>0.6309010241597218</v>
       </c>
       <c r="E31">
-        <v>0.6068894101078016</v>
+        <v>0.6068894103704627</v>
       </c>
       <c r="F31">
-        <v>0.6233681569294257</v>
+        <v>0.62336815676585</v>
       </c>
       <c r="G31">
-        <v>0.6146517710490463</v>
+        <v>0.6146517709168022</v>
       </c>
       <c r="H31">
-        <v>0.5991730024421331</v>
+        <v>0.5991730026249036</v>
       </c>
       <c r="I31">
-        <v>0.5843160841940586</v>
+        <v>0.5843160820783305</v>
       </c>
       <c r="J31">
-        <v>0.5938111638149998</v>
+        <v>0.593811158970998</v>
       </c>
       <c r="K31">
-        <v>0.5921686726585854</v>
+        <v>0.5921686727550822</v>
       </c>
       <c r="L31">
-        <v>0.6111347055481133</v>
+        <v>0.6111346976562323</v>
       </c>
       <c r="M31">
-        <v>0.6100952273588983</v>
+        <v>0.610095216696096</v>
       </c>
       <c r="N31">
-        <v>0.6060348789017382</v>
+        <v>0.6060348731752</v>
       </c>
       <c r="O31">
-        <v>0.5850981910248567</v>
+        <v>0.5850981882230022</v>
       </c>
       <c r="P31">
-        <v>0.5791066047757251</v>
+        <v>0.5791066047116468</v>
       </c>
       <c r="Q31">
-        <v>0.5603870836899643</v>
+        <v>0.5603871179230554</v>
       </c>
     </row>
     <row r="32">
@@ -2101,49 +2101,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.5981123547563237</v>
+        <v>0.598112354769437</v>
       </c>
       <c r="D32">
-        <v>0.6291055290759393</v>
+        <v>0.6291055289728128</v>
       </c>
       <c r="E32">
-        <v>0.6009622113891995</v>
+        <v>0.6009622116216372</v>
       </c>
       <c r="F32">
-        <v>0.6212864783545687</v>
+        <v>0.6212864780706899</v>
       </c>
       <c r="G32">
-        <v>0.6103563291087259</v>
+        <v>0.610356329378467</v>
       </c>
       <c r="H32">
-        <v>0.5907734513579633</v>
+        <v>0.5907734487124543</v>
       </c>
       <c r="I32">
-        <v>0.5727002799236942</v>
+        <v>0.5727002771021867</v>
       </c>
       <c r="J32">
-        <v>0.5804865279366238</v>
+        <v>0.5804865172042875</v>
       </c>
       <c r="K32">
-        <v>0.5863231234250736</v>
+        <v>0.5863231158906607</v>
       </c>
       <c r="L32">
-        <v>0.6061586030865854</v>
+        <v>0.6061585990148001</v>
       </c>
       <c r="M32">
-        <v>0.6018881855054367</v>
+        <v>0.6018881782907843</v>
       </c>
       <c r="N32">
-        <v>0.5838908835157637</v>
+        <v>0.5838908926505972</v>
       </c>
       <c r="O32">
-        <v>0.5547389273358089</v>
+        <v>0.5547389480910545</v>
       </c>
       <c r="P32">
-        <v>0.5577710207640508</v>
+        <v>0.5577710592313925</v>
       </c>
       <c r="Q32">
-        <v>0.5294600159933327</v>
+        <v>0.5294600769274689</v>
       </c>
     </row>
     <row r="33">
@@ -2156,49 +2156,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.5982819530010279</v>
+        <v>0.5982819530199538</v>
       </c>
       <c r="D33">
-        <v>0.6299211515938394</v>
+        <v>0.629921151511969</v>
       </c>
       <c r="E33">
-        <v>0.6059829623311739</v>
+        <v>0.6059829625650824</v>
       </c>
       <c r="F33">
-        <v>0.62316706090326</v>
+        <v>0.6231670606230256</v>
       </c>
       <c r="G33">
-        <v>0.6128184524604449</v>
+        <v>0.6128184526644753</v>
       </c>
       <c r="H33">
-        <v>0.5935250159643283</v>
+        <v>0.5935250178907702</v>
       </c>
       <c r="I33">
-        <v>0.5730318453597777</v>
+        <v>0.5730318427407941</v>
       </c>
       <c r="J33">
-        <v>0.5851666795119749</v>
+        <v>0.5851666694167904</v>
       </c>
       <c r="K33">
-        <v>0.5924257710150699</v>
+        <v>0.5924257699371845</v>
       </c>
       <c r="L33">
-        <v>0.6116110271146136</v>
+        <v>0.611611022037692</v>
       </c>
       <c r="M33">
-        <v>0.6105209588876502</v>
+        <v>0.6105209559104258</v>
       </c>
       <c r="N33">
-        <v>0.5959755711617106</v>
+        <v>0.5959755769949142</v>
       </c>
       <c r="O33">
-        <v>0.5685048840214203</v>
+        <v>0.5685048956935684</v>
       </c>
       <c r="P33">
-        <v>0.5681073974235353</v>
+        <v>0.5681074181707575</v>
       </c>
       <c r="Q33">
-        <v>0.5432852410470904</v>
+        <v>0.5432852990750039</v>
       </c>
     </row>
     <row r="34">
@@ -2211,49 +2211,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.5965466009276867</v>
+        <v>0.5965466009447441</v>
       </c>
       <c r="D34">
-        <v>0.6287520800128935</v>
+        <v>0.6287520799100407</v>
       </c>
       <c r="E34">
-        <v>0.6022126057586739</v>
+        <v>0.6022126059719956</v>
       </c>
       <c r="F34">
-        <v>0.6209156080989726</v>
+        <v>0.6209156078250304</v>
       </c>
       <c r="G34">
-        <v>0.6107307603157536</v>
+        <v>0.6107307601827909</v>
       </c>
       <c r="H34">
-        <v>0.5962983241614153</v>
+        <v>0.5962983234494537</v>
       </c>
       <c r="I34">
-        <v>0.5772241078608343</v>
+        <v>0.5772241067183475</v>
       </c>
       <c r="J34">
-        <v>0.5892348795007754</v>
+        <v>0.5892348692123011</v>
       </c>
       <c r="K34">
-        <v>0.5933550789970321</v>
+        <v>0.5933550713335545</v>
       </c>
       <c r="L34">
-        <v>0.6143521292366032</v>
+        <v>0.6143521240449841</v>
       </c>
       <c r="M34">
-        <v>0.6091929992294639</v>
+        <v>0.6091929936897863</v>
       </c>
       <c r="N34">
-        <v>0.5945637108168182</v>
+        <v>0.5945637101332762</v>
       </c>
       <c r="O34">
-        <v>0.5696233327867892</v>
+        <v>0.5696233434600699</v>
       </c>
       <c r="P34">
-        <v>0.5741952625943242</v>
+        <v>0.5741952828594874</v>
       </c>
       <c r="Q34">
-        <v>0.5462957336010502</v>
+        <v>0.5462957806151448</v>
       </c>
     </row>
     <row r="35">
@@ -2266,49 +2266,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.5983205485742765</v>
+        <v>0.5983205485870157</v>
       </c>
       <c r="D35">
-        <v>0.6308585888014309</v>
+        <v>0.6308585887055151</v>
       </c>
       <c r="E35">
-        <v>0.607097806784521</v>
+        <v>0.6070978069627303</v>
       </c>
       <c r="F35">
-        <v>0.6230476406661273</v>
+        <v>0.6230476403731492</v>
       </c>
       <c r="G35">
-        <v>0.6147740012290861</v>
+        <v>0.6147740016504871</v>
       </c>
       <c r="H35">
-        <v>0.598632636116593</v>
+        <v>0.5986326355648045</v>
       </c>
       <c r="I35">
-        <v>0.5839370089065129</v>
+        <v>0.5839370073944814</v>
       </c>
       <c r="J35">
-        <v>0.5938867622313976</v>
+        <v>0.5938867526996555</v>
       </c>
       <c r="K35">
-        <v>0.5927354767318285</v>
+        <v>0.5927354695279402</v>
       </c>
       <c r="L35">
-        <v>0.6118052554052151</v>
+        <v>0.6118052512800932</v>
       </c>
       <c r="M35">
-        <v>0.610907119226102</v>
+        <v>0.6109071101902164</v>
       </c>
       <c r="N35">
-        <v>0.600493287904543</v>
+        <v>0.6004932815497845</v>
       </c>
       <c r="O35">
-        <v>0.5755411555177274</v>
+        <v>0.5755411491699082</v>
       </c>
       <c r="P35">
-        <v>0.5784789277507388</v>
+        <v>0.5784791585963421</v>
       </c>
       <c r="Q35">
-        <v>0.5553502059021389</v>
+        <v>0.5553502431862443</v>
       </c>
     </row>
     <row r="36">
@@ -2321,49 +2321,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.5973986270969242</v>
+        <v>0.5973986271272735</v>
       </c>
       <c r="D36">
-        <v>0.6302191615886715</v>
+        <v>0.6302191615234176</v>
       </c>
       <c r="E36">
-        <v>0.6047729413450942</v>
+        <v>0.6047729416156713</v>
       </c>
       <c r="F36">
-        <v>0.6219527045366355</v>
+        <v>0.6219527044111151</v>
       </c>
       <c r="G36">
-        <v>0.6131057187118798</v>
+        <v>0.6131057188604494</v>
       </c>
       <c r="H36">
-        <v>0.5971983464715483</v>
+        <v>0.5971983462169966</v>
       </c>
       <c r="I36">
-        <v>0.5781335197242551</v>
+        <v>0.5781335191043684</v>
       </c>
       <c r="J36">
-        <v>0.5901379194476916</v>
+        <v>0.5901379115137048</v>
       </c>
       <c r="K36">
-        <v>0.592303227498431</v>
+        <v>0.5923032210923552</v>
       </c>
       <c r="L36">
-        <v>0.6097338329288984</v>
+        <v>0.609733825980431</v>
       </c>
       <c r="M36">
-        <v>0.6073023305435077</v>
+        <v>0.6073023201781841</v>
       </c>
       <c r="N36">
-        <v>0.605429360631802</v>
+        <v>0.6054293660578043</v>
       </c>
       <c r="O36">
-        <v>0.5818376264613488</v>
+        <v>0.581837613723709</v>
       </c>
       <c r="P36">
-        <v>0.5801445912106643</v>
+        <v>0.5801445924918328</v>
       </c>
       <c r="Q36">
-        <v>0.5644621179764001</v>
+        <v>0.5644621277452242</v>
       </c>
     </row>
     <row r="37">
@@ -2376,49 +2376,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.6319831478123158</v>
+        <v>0.6319831471719984</v>
       </c>
       <c r="D37">
-        <v>0.6298334709520158</v>
+        <v>0.6298334711834668</v>
       </c>
       <c r="E37">
-        <v>0.6293310574607023</v>
+        <v>0.629331056757214</v>
       </c>
       <c r="F37">
-        <v>0.6281425149536812</v>
+        <v>0.6281425106140773</v>
       </c>
       <c r="G37">
-        <v>0.5976180638805242</v>
+        <v>0.5976180479799079</v>
       </c>
       <c r="H37">
-        <v>0.5696571615683536</v>
+        <v>0.5696571400078868</v>
       </c>
       <c r="I37">
-        <v>0.5861980571914297</v>
+        <v>0.5861980804170525</v>
       </c>
       <c r="J37">
-        <v>0.5751892001982707</v>
+        <v>0.5751892306182468</v>
       </c>
       <c r="K37">
-        <v>0.5625180062419399</v>
+        <v>0.5625180931363116</v>
       </c>
       <c r="L37">
-        <v>0.5272172628910261</v>
+        <v>0.5272173990441194</v>
       </c>
       <c r="M37">
-        <v>0.4815660284953596</v>
+        <v>0.4815662985139236</v>
       </c>
       <c r="N37">
-        <v>0.4223315551744488</v>
+        <v>0.4223290296348496</v>
       </c>
       <c r="O37">
-        <v>0.3345535787313146</v>
+        <v>0.3345522124439876</v>
       </c>
       <c r="P37">
-        <v>0.2778819866403686</v>
+        <v>0.2778823119793755</v>
       </c>
       <c r="Q37">
-        <v>0.2228010330702021</v>
+        <v>0.2228014045769923</v>
       </c>
     </row>
     <row r="38">
@@ -2431,49 +2431,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.6283314248539937</v>
+        <v>0.6283314241440906</v>
       </c>
       <c r="D38">
-        <v>0.6295143037516912</v>
+        <v>0.6295143033188001</v>
       </c>
       <c r="E38">
-        <v>0.6321178416584672</v>
+        <v>0.6321178407323635</v>
       </c>
       <c r="F38">
-        <v>0.6325210862943751</v>
+        <v>0.632521082711178</v>
       </c>
       <c r="G38">
-        <v>0.6177942424464151</v>
+        <v>0.6177942374963239</v>
       </c>
       <c r="H38">
-        <v>0.6010430435740617</v>
+        <v>0.601043031459777</v>
       </c>
       <c r="I38">
-        <v>0.599325372080844</v>
+        <v>0.5993253632543724</v>
       </c>
       <c r="J38">
-        <v>0.5714472422559815</v>
+        <v>0.5714472435902768</v>
       </c>
       <c r="K38">
-        <v>0.5102644164450149</v>
+        <v>0.5102644107250786</v>
       </c>
       <c r="L38">
-        <v>0.482411851869546</v>
+        <v>0.4824118553709781</v>
       </c>
       <c r="M38">
-        <v>0.4698564720756657</v>
+        <v>0.4698564949056742</v>
       </c>
       <c r="N38">
-        <v>0.4908699552215187</v>
+        <v>0.4908700091848545</v>
       </c>
       <c r="O38">
-        <v>0.5086184798112612</v>
+        <v>0.5086186215991663</v>
       </c>
       <c r="P38">
-        <v>0.4892998881320823</v>
+        <v>0.4893001287340341</v>
       </c>
       <c r="Q38">
-        <v>0.4679414453226308</v>
+        <v>0.4679416702948714</v>
       </c>
     </row>
     <row r="39">
@@ -2486,49 +2486,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.628816545312174</v>
+        <v>0.6288165445724452</v>
       </c>
       <c r="D39">
-        <v>0.6284350182280195</v>
+        <v>0.6284350176232585</v>
       </c>
       <c r="E39">
-        <v>0.6326256329068237</v>
+        <v>0.632625631065846</v>
       </c>
       <c r="F39">
-        <v>0.6316155965162789</v>
+        <v>0.6316155929866665</v>
       </c>
       <c r="G39">
-        <v>0.6173431115136748</v>
+        <v>0.6173431069269782</v>
       </c>
       <c r="H39">
-        <v>0.6031438663670634</v>
+        <v>0.6031438549825928</v>
       </c>
       <c r="I39">
-        <v>0.615075419879871</v>
+        <v>0.6150754125092321</v>
       </c>
       <c r="J39">
-        <v>0.5974202708609596</v>
+        <v>0.597420263147986</v>
       </c>
       <c r="K39">
-        <v>0.5245460585794742</v>
+        <v>0.5245460550648302</v>
       </c>
       <c r="L39">
-        <v>0.5022953174739677</v>
+        <v>0.5022953164342936</v>
       </c>
       <c r="M39">
-        <v>0.4887054060607111</v>
+        <v>0.4887054041410626</v>
       </c>
       <c r="N39">
-        <v>0.4817065181585592</v>
+        <v>0.4817065195506103</v>
       </c>
       <c r="O39">
-        <v>0.4830602051810329</v>
+        <v>0.4830602253227006</v>
       </c>
       <c r="P39">
-        <v>0.4819289188066779</v>
+        <v>0.4819289672739041</v>
       </c>
       <c r="Q39">
-        <v>0.4437121109955692</v>
+        <v>0.4437121669647044</v>
       </c>
     </row>
     <row r="40">
@@ -2541,49 +2541,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.5935608743064132</v>
+        <v>0.5935608726587871</v>
       </c>
       <c r="D40">
-        <v>0.5857924748211119</v>
+        <v>0.5857924749423371</v>
       </c>
       <c r="E40">
-        <v>0.5697095367490579</v>
+        <v>0.5697095397470512</v>
       </c>
       <c r="F40">
-        <v>0.6031674254669076</v>
+        <v>0.6031674298744828</v>
       </c>
       <c r="G40">
-        <v>0.6210334881073715</v>
+        <v>0.6210334912288265</v>
       </c>
       <c r="H40">
-        <v>0.5927822152376228</v>
+        <v>0.5927822169636211</v>
       </c>
       <c r="I40">
-        <v>0.5553813160123359</v>
+        <v>0.5553813226852292</v>
       </c>
       <c r="J40">
-        <v>0.5221998150127227</v>
+        <v>0.5221998427435709</v>
       </c>
       <c r="K40">
-        <v>0.5034864855964408</v>
+        <v>0.5034865628896729</v>
       </c>
       <c r="L40">
-        <v>0.4818498928032821</v>
+        <v>0.481850005458966</v>
       </c>
       <c r="M40">
-        <v>0.439959500999161</v>
+        <v>0.4399596408571014</v>
       </c>
       <c r="N40">
-        <v>0.3577729313257353</v>
+        <v>0.3577730965142043</v>
       </c>
       <c r="O40">
-        <v>0.255366874017857</v>
+        <v>0.2553670951741511</v>
       </c>
       <c r="P40">
-        <v>0.1567117136470396</v>
+        <v>0.1567120631394307</v>
       </c>
       <c r="Q40">
-        <v>0.1060963969453542</v>
+        <v>0.1060968731519982</v>
       </c>
     </row>
     <row r="41">
@@ -2596,49 +2596,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.5857595008498613</v>
+        <v>0.5857595010399009</v>
       </c>
       <c r="D41">
-        <v>0.6113013615069568</v>
+        <v>0.6113013626661949</v>
       </c>
       <c r="E41">
-        <v>0.5530348672991638</v>
+        <v>0.5530348717811173</v>
       </c>
       <c r="F41">
-        <v>0.5453535789350331</v>
+        <v>0.5453535850254324</v>
       </c>
       <c r="G41">
-        <v>0.5570333365996577</v>
+        <v>0.5570333508886635</v>
       </c>
       <c r="H41">
-        <v>0.5082074662141096</v>
+        <v>0.5082074934590594</v>
       </c>
       <c r="I41">
-        <v>0.4966989580261165</v>
+        <v>0.4966990010092699</v>
       </c>
       <c r="J41">
-        <v>0.4902622556603111</v>
+        <v>0.4902623091243979</v>
       </c>
       <c r="K41">
-        <v>0.463540778257415</v>
+        <v>0.4635408500581236</v>
       </c>
       <c r="L41">
-        <v>0.430264654306641</v>
+        <v>0.4302647449174605</v>
       </c>
       <c r="M41">
-        <v>0.3765677302659472</v>
+        <v>0.3765678666805813</v>
       </c>
       <c r="N41">
-        <v>0.2818984390508165</v>
+        <v>0.2818986387367317</v>
       </c>
       <c r="O41">
-        <v>0.2436968373199161</v>
+        <v>0.2436970828284237</v>
       </c>
       <c r="P41">
-        <v>0.2038701690763918</v>
+        <v>0.203870462549094</v>
       </c>
       <c r="Q41">
-        <v>0.1767702997632739</v>
+        <v>0.1767706320960028</v>
       </c>
     </row>
     <row r="42">
@@ -2651,49 +2651,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.4617035365669464</v>
+        <v>0.4617035317337</v>
       </c>
       <c r="D42">
-        <v>0.610181922835112</v>
+        <v>0.6101819229480125</v>
       </c>
       <c r="E42">
-        <v>0.5724653041328985</v>
+        <v>0.5724653056750378</v>
       </c>
       <c r="F42">
-        <v>0.5210364606148404</v>
+        <v>0.5210364642675039</v>
       </c>
       <c r="G42">
-        <v>0.5436869667195766</v>
+        <v>0.5436869625076471</v>
       </c>
       <c r="H42">
-        <v>0.5600078884905455</v>
+        <v>0.5600078763714641</v>
       </c>
       <c r="I42">
-        <v>0.5405200881409535</v>
+        <v>0.5405200710155644</v>
       </c>
       <c r="J42">
-        <v>0.4778467604889289</v>
+        <v>0.4778467589405594</v>
       </c>
       <c r="K42">
-        <v>0.4092466087643933</v>
+        <v>0.4092465830072781</v>
       </c>
       <c r="L42">
-        <v>0.3623469649915194</v>
+        <v>0.3623469258968839</v>
       </c>
       <c r="M42">
-        <v>0.3221431356929617</v>
+        <v>0.3221430976391101</v>
       </c>
       <c r="N42">
-        <v>0.2964890701855939</v>
+        <v>0.2964889975984593</v>
       </c>
       <c r="O42">
-        <v>0.2711089765873933</v>
+        <v>0.2711088858169266</v>
       </c>
       <c r="P42">
-        <v>0.2259799655467406</v>
+        <v>0.2259798400503988</v>
       </c>
       <c r="Q42">
-        <v>0.1760857710788321</v>
+        <v>0.1760856395689323</v>
       </c>
     </row>
     <row r="43">
@@ -2706,49 +2706,49 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.612532829099214</v>
+        <v>0.6125328292952568</v>
       </c>
       <c r="D43">
-        <v>0.5976855507179578</v>
+        <v>0.5976855511267729</v>
       </c>
       <c r="E43">
-        <v>0.5838310903579925</v>
+        <v>0.583831091158178</v>
       </c>
       <c r="F43">
-        <v>0.5917854990805922</v>
+        <v>0.5917854992086604</v>
       </c>
       <c r="G43">
-        <v>0.5499871159851841</v>
+        <v>0.5499871151429566</v>
       </c>
       <c r="H43">
-        <v>0.546323083656601</v>
+        <v>0.5463230825735366</v>
       </c>
       <c r="I43">
-        <v>0.5200912033896373</v>
+        <v>0.5200912031468977</v>
       </c>
       <c r="J43">
-        <v>0.4995073213625885</v>
+        <v>0.4995073269353105</v>
       </c>
       <c r="K43">
-        <v>0.4582997340494743</v>
+        <v>0.4582997447414868</v>
       </c>
       <c r="L43">
-        <v>0.3990492084740457</v>
+        <v>0.3990492165420338</v>
       </c>
       <c r="M43">
-        <v>0.3391063539165919</v>
+        <v>0.3391063526096236</v>
       </c>
       <c r="N43">
-        <v>0.2891660743689997</v>
+        <v>0.2891660584863238</v>
       </c>
       <c r="O43">
-        <v>0.2705505521415412</v>
+        <v>0.2705505427638978</v>
       </c>
       <c r="P43">
-        <v>0.2667886983454261</v>
+        <v>0.2667886936276218</v>
       </c>
       <c r="Q43">
-        <v>0.2501311960359755</v>
+        <v>0.2501312055311742</v>
       </c>
     </row>
   </sheetData>
